--- a/tables/wave_pars.xlsx
+++ b/tables/wave_pars.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthipsey/AED Dropbox/Matt Hipsey/GitHub/cdm-science/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BF4747-1043-0342-A4A5-8177A914F18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFE4BCE-E70F-2943-B968-785F9BB6DE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="4820" windowWidth="19560" windowHeight="16460" activeTab="1" xr2:uid="{DECC0CF8-79EF-43B2-948C-02F9DA64B271}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
   <si>
     <t>Parameter</t>
   </si>
@@ -280,6 +281,15 @@
   </si>
   <si>
     <t>Refer to Table \@ref(tab:dev-zonepars)</t>
+  </si>
+  <si>
+    <t>POM</t>
+  </si>
+  <si>
+    <t>SS1:Fines</t>
+  </si>
+  <si>
+    <t>SS2:Sand</t>
   </si>
 </sst>
 </file>
@@ -413,9 +423,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -453,7 +463,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -559,7 +569,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -701,7 +711,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -820,7 +830,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9092AC5-A5D9-EC4A-8726-15551DC79124}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -840,6 +850,166 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4">
+        <v>0.02</v>
+      </c>
+      <c r="G4">
+        <v>0.02</v>
+      </c>
+      <c r="H4">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5">
+        <v>0.05</v>
+      </c>
+      <c r="G5">
+        <v>0.15</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACAF912C-235B-414F-9479-6614E393D8D1}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G1" t="s">

--- a/tables/wave_pars.xlsx
+++ b/tables/wave_pars.xlsx
@@ -1,41 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFE4BCE-E70F-2943-B968-785F9BB6DE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="4820" windowWidth="19560" windowHeight="16460" activeTab="1" xr2:uid="{DECC0CF8-79EF-43B2-948C-02F9DA64B271}"/>
+    <workbookView xWindow="3900" yWindow="4820" windowWidth="19560" windowHeight="16460" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Parameter</t>
   </si>
@@ -291,12 +271,115 @@
   <si>
     <t>SS2:Sand</t>
   </si>
+  <si>
+    <t xml:space="preserve">Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Literature.range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS1:Fines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS2:Sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\Theta_{SS}^{settling}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settling sub-model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V_s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sedimentation velocity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m/d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 – 104 $^a$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.55 $^e$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-110.0 $^e$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.88 $^e$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g/m^2/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical shear stress for resuspension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/m^2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linked to NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_{s,s}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">particle fraction within the sediment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w/w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refer to Table \@ref(tab:dev-zonepars)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-110.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.88</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,14 +391,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -347,10 +427,8 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -360,7 +438,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -369,22 +446,17 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -404,7 +476,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,11 +790,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B82B77B-C9BA-4627-B3DE-F5D84FB8884D}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="17.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="31" customHeight="1">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -742,7 +814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="31" customHeight="1">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -758,11 +830,11 @@
       <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="4" t="n">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="17" customHeight="1">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -778,11 +850,11 @@
       <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="4" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="31" customHeight="1">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -798,11 +870,11 @@
       <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="17" customHeight="1">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -818,99 +890,100 @@
       <c r="E5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="4" t="n">
         <v>0.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9092AC5-A5D9-EC4A-8726-15551DC79124}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="17.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="16" customHeight="1">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E2"/>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -919,81 +992,83 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>48</v>
       </c>
-      <c r="F4">
-        <v>0.02</v>
-      </c>
-      <c r="G4">
-        <v>0.02</v>
-      </c>
-      <c r="H4">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>57</v>
       </c>
-      <c r="F5">
-        <v>0.05</v>
-      </c>
-      <c r="G5">
-        <v>0.15</v>
-      </c>
-      <c r="H5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="E6"/>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACAF912C-235B-414F-9479-6614E393D8D1}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="31" customHeight="1">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1019,7 +1094,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1042,7 +1117,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1055,17 +1130,17 @@
       <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="5" t="n">
         <v>1.5999999999999999E-6</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="5" t="n">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="5" t="n">
         <v>6.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1078,17 +1153,17 @@
       <c r="D4" t="s">
         <v>41</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>1500</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1600</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1800</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1114,7 +1189,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1130,17 +1205,17 @@
       <c r="E6" t="s">
         <v>48</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>0.02</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>0.02</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1156,17 +1231,17 @@
       <c r="E7" t="s">
         <v>57</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>0.05</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>0.15</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1189,7 +1264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1202,17 +1277,17 @@
       <c r="D9" t="s">
         <v>47</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>6.3E-2</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>0.06</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1225,17 +1300,18 @@
       <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>